--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484298_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484298_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.7006</v>
+        <v>5.1813</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1467</v>
+        <v>3.4095</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5539</v>
+        <v>1.7718</v>
       </c>
       <c r="G2" t="n">
         <v>2.8523</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6829</v>
+        <v>-0.2022</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0289</v>
+        <v>-0.7661</v>
       </c>
       <c r="U2" t="n">
-        <v>0.346</v>
+        <v>0.5639</v>
       </c>
       <c r="V2" t="n">
         <v>1.1638</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8349</v>
+        <v>2.9753</v>
       </c>
       <c r="E3" t="n">
-        <v>0.122</v>
+        <v>0.3442</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7129</v>
+        <v>2.6312</v>
       </c>
       <c r="G3" t="n">
         <v>1.6981</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.426</v>
+        <v>-0.2855</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.271</v>
+        <v>-1.0488</v>
       </c>
       <c r="U3" t="n">
-        <v>0.845</v>
+        <v>0.7633</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0369</v>
+        <v>1.109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4159</v>
+        <v>0.6786</v>
       </c>
       <c r="F4" t="n">
-        <v>0.621</v>
+        <v>0.4304</v>
       </c>
       <c r="G4" t="n">
         <v>4.5101</v>
@@ -766,13 +766,13 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.196</v>
+        <v>-0.1239</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6052</v>
+        <v>-0.3425</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4093</v>
+        <v>0.2186</v>
       </c>
       <c r="V4" t="n">
         <v>-2.1052</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2627</v>
+        <v>-0.2082</v>
       </c>
       <c r="E5" t="n">
         <v>-0.7547</v>
       </c>
       <c r="F5" t="n">
-        <v>0.492</v>
+        <v>0.5465</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1642</v>
@@ -844,13 +844,13 @@
         <v>0.1953</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2938</v>
+        <v>-0.2394</v>
       </c>
       <c r="T5" t="n">
         <v>-0.121</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1728</v>
+        <v>-0.1183</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3525</v>
+        <v>-1.2449</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4173</v>
+        <v>-2.0646</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0648</v>
+        <v>0.8197</v>
       </c>
       <c r="G6" t="n">
         <v>0.6294</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9949</v>
+        <v>0.1025</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4541</v>
+        <v>-0.1931</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5407</v>
+        <v>0.2956</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6093</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6494</v>
+        <v>-1.2525</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9353</v>
+        <v>0.3953</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2859</v>
+        <v>-1.6478</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6471</v>
+        <v>-1.6021</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3751</v>
+        <v>-1.671</v>
       </c>
       <c r="I7" t="n">
-        <v>0.728</v>
+        <v>0.0689</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0938</v>
+        <v>0.325</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4439</v>
+        <v>-0.284</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5377</v>
+        <v>0.609</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7409</v>
+        <v>-1.9271</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9312</v>
+        <v>-1.387</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8097</v>
+        <v>-0.5401</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3884</v>
+        <v>0.119</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0756</v>
+        <v>-0.2069</v>
       </c>
       <c r="U7" t="n">
-        <v>1.464</v>
+        <v>0.3259</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8579</v>
+        <v>-1.8514</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2919</v>
+        <v>-1.5109</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5661</v>
+        <v>-0.3405</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6021</v>
+        <v>-1.6471</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.671</v>
+        <v>-2.3751</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0689</v>
+        <v>0.728</v>
       </c>
       <c r="J8" t="n">
-        <v>0.325</v>
+        <v>1.0938</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.284</v>
+        <v>-0.4439</v>
       </c>
       <c r="L8" t="n">
-        <v>0.609</v>
+        <v>1.5377</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9271</v>
+        <v>-2.7409</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.387</v>
+        <v>-1.9312</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5401</v>
+        <v>-0.8097</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4865</v>
+        <v>0.1864</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8941</v>
+        <v>-0.6512</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4076</v>
+        <v>0.8376</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9908</v>
+        <v>-2.1247</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6353</v>
+        <v>-1.8781</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3555</v>
+        <v>-0.2466</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5263</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1557</v>
+        <v>-0.2896</v>
       </c>
       <c r="T9" t="n">
-        <v>0.311</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4667</v>
+        <v>-0.3577</v>
       </c>
       <c r="V9" t="n">
         <v>0.2772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3276</v>
+        <v>-2.1613</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8205</v>
+        <v>-1.1446</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.507</v>
+        <v>-1.0168</v>
       </c>
       <c r="G10" t="n">
         <v>2.3885</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1766</v>
+        <v>-0.0103</v>
       </c>
       <c r="T10" t="n">
-        <v>0.212</v>
+        <v>-0.112</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3886</v>
+        <v>0.1016</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8583</v>
+        <v>-3.2415</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8134</v>
+        <v>-3.5506</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.045</v>
+        <v>0.3091</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1861</v>
@@ -1312,13 +1312,13 @@
         <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3597</v>
+        <v>-0.7429</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0151</v>
+        <v>-0.7524</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3446</v>
+        <v>0.0095</v>
       </c>
       <c r="V11" t="n">
         <v>0.0549</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7268</v>
+        <v>-2.818899999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9838</v>
+        <v>-6.075900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2569</v>
+        <v>3.257</v>
       </c>
       <c r="G12" t="n">
         <v>5.9526</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.143600000000001</v>
+        <v>-2.1436</v>
       </c>
       <c r="I12" t="n">
         <v>8.096200000000001</v>
@@ -1390,13 +1390,13 @@
         <v>11.7204</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3939</v>
+        <v>-1.4859</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.033799999999999</v>
+        <v>-4.1259</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6399</v>
+        <v>2.64</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3786</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. MAYO SCHWANDT</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.2243</v>
+        <v>6.1975</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5746</v>
+        <v>4.4418</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6497</v>
+        <v>1.7557</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4765</v>
+        <v>1.6761</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0128</v>
+        <v>0.8404</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5363</v>
+        <v>0.8358</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3202</v>
+        <v>3.585</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5066</v>
+        <v>1.1294</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.1863</v>
+        <v>2.4556</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8437</v>
+        <v>-1.9089</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4937</v>
+        <v>-0.2891</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.35</v>
+        <v>-1.6198</v>
       </c>
       <c r="P13" t="n">
         <v>1.7581</v>
@@ -1468,19 +1468,19 @@
         <v>2.7348</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1617</v>
+        <v>0.326</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5969</v>
+        <v>-0.6038</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.9298</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8279</v>
+        <v>2.4373</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8279</v>
+        <v>2.4373</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>I. MAYO SCHWANDT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0551</v>
+        <v>6.1685</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8351</v>
+        <v>4.5746</v>
       </c>
       <c r="F14" t="n">
-        <v>2.22</v>
+        <v>1.5939</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6761</v>
+        <v>2.4765</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8404</v>
+        <v>5.0128</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8358</v>
+        <v>-2.5363</v>
       </c>
       <c r="J14" t="n">
-        <v>3.585</v>
+        <v>4.3202</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1294</v>
+        <v>5.5066</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4556</v>
+        <v>-1.1863</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9089</v>
+        <v>-1.8437</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2891</v>
+        <v>-0.4937</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6198</v>
+        <v>-1.35</v>
       </c>
       <c r="P14" t="n">
         <v>1.7581</v>
@@ -1546,19 +1546,19 @@
         <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1837</v>
+        <v>0.1059</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2105</v>
+        <v>-0.5969</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3941</v>
+        <v>0.7028</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4373</v>
+        <v>1.8279</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4373</v>
+        <v>1.8279</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4851</v>
+        <v>4.4878</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0904</v>
+        <v>3.686</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3947</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>3.9575</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0551</v>
+        <v>0.0578</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1043</v>
+        <v>-0.5088</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1594</v>
+        <v>0.5666</v>
       </c>
       <c r="V15" t="n">
         <v>0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2329</v>
+        <v>2.4083</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6922</v>
+        <v>1.0856</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5406</v>
+        <v>1.3227</v>
       </c>
       <c r="G16" t="n">
         <v>2.7591</v>
@@ -1702,13 +1702,13 @@
         <v>0.9767</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4505</v>
+        <v>0.6259</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8035</v>
+        <v>0.1968</v>
       </c>
       <c r="U16" t="n">
-        <v>0.647</v>
+        <v>0.4291</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7504</v>
+        <v>-0.0197</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1102</v>
+        <v>-0.4965</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6402</v>
+        <v>0.4768</v>
       </c>
       <c r="G17" t="n">
         <v>-1.1216</v>
@@ -1780,13 +1780,13 @@
         <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4813</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6824</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.6355</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4959</v>
+        <v>-0.3131</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9362</v>
+        <v>-0.8351</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4403</v>
+        <v>0.522</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6385</v>
@@ -1858,13 +1858,13 @@
         <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2481</v>
+        <v>-0.0653</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3026</v>
+        <v>-0.2015</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0545</v>
+        <v>0.1362</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2649</v>
+        <v>-1.0093</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5899</v>
+        <v>-0.4961</v>
       </c>
       <c r="F19" t="n">
-        <v>0.325</v>
+        <v>-0.5131</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8875</v>
+        <v>-2.0243</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8222</v>
+        <v>-0.9992</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0653</v>
+        <v>-1.0251</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5378</v>
+        <v>-0.4561</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.5104</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6603</v>
+        <v>0.0543</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3498</v>
+        <v>-1.5682</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0553</v>
+        <v>-0.4889</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4051</v>
+        <v>-1.0793</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3957</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0522</v>
+        <v>-0.282</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4479</v>
+        <v>0.2737</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5914</v>
+        <v>-1.0471</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6984</v>
+        <v>-1.5899</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8931</v>
+        <v>0.5429</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.0243</v>
+        <v>-1.8875</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9992</v>
+        <v>-0.8222</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0251</v>
+        <v>-1.0653</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4561</v>
+        <v>-1.5378</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5104</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0543</v>
+        <v>-0.6603</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5682</v>
+        <v>-0.3498</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4889</v>
+        <v>0.0553</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0793</v>
+        <v>-0.4051</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5904</v>
+        <v>0.6136</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4842</v>
+        <v>-0.0522</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1062</v>
+        <v>0.6657</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2186</v>
+        <v>-0.5545</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9018</v>
+        <v>-2.3066</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2971</v>
+        <v>-1.8926</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6047</v>
+        <v>-0.414</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4414</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2966</v>
+        <v>0.2985</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4237</v>
+        <v>-0.0192</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1271</v>
+        <v>0.3177</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1638</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4882</v>
+        <v>-3.2989</v>
       </c>
       <c r="E22" t="n">
         <v>-3.6404</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1523</v>
+        <v>0.3416</v>
       </c>
       <c r="G22" t="n">
         <v>-4.3472</v>
@@ -2170,13 +2170,13 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0776</v>
+        <v>0.2669</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3548</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4324</v>
+        <v>0.6217</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2787</v>
+        <v>-6.8664</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.397399999999999</v>
+        <v>-8.094099999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1187</v>
+        <v>1.2277</v>
       </c>
       <c r="G23" t="n">
         <v>-5.3611</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2767</v>
+        <v>0.1356</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5969</v>
+        <v>-0.2935</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3201</v>
+        <v>0.4291</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6642</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.726899999999998</v>
+        <v>4.401000000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2569</v>
+        <v>-3.256699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>6.983699999999999</v>
+        <v>7.658099999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-5.952400000000002</v>
@@ -2326,13 +2326,13 @@
         <v>15.6275</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3938</v>
+        <v>3.0679</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.640199999999999</v>
+        <v>-2.6401</v>
       </c>
       <c r="U24" t="n">
-        <v>5.0338</v>
+        <v>5.7079</v>
       </c>
       <c r="V24" t="n">
         <v>3.3785</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484298_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484298_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.7731</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.0549</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,11 +1462,12 @@
       <c r="X12" t="n">
         <v>-4.764699999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1484,6 +1540,11 @@
       </c>
       <c r="X13" t="n">
         <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,11 +2288,16 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2264,6 +2370,11 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484298_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-1.3862</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
